--- a/backend/src/chatBot/2026_ KỊCH BẢN CHĂM SÓC.xlsx
+++ b/backend/src/chatBot/2026_ KỊCH BẢN CHĂM SÓC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Render\Chatbot\backend\src\chatBot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AFD5887-3C4A-46CB-B916-4F0FCE1500A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00F51967-23ED-4F4F-AD66-EDE9A827BDA2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="236">
   <si>
     <t>https://xts.donga.edu.vn/dkhocbong/register</t>
   </si>
@@ -60,13 +60,6 @@
     <t>Trả lời</t>
   </si>
   <si>
-    <t>Đính kèm (hình, link, File)...</t>
-  </si>
-  <si>
-    <t>Mở rộng tương tác
-Câu hỏi gợi mở sau trả lời (Tùy tình hình)</t>
-  </si>
-  <si>
     <t>Bắt đầu</t>
   </si>
   <si>
@@ -83,19 +76,11 @@
     <t>Trường còn xét tuyển không?</t>
   </si>
   <si>
-    <t>Admin chào ban, 
-ĐH Đông Á xét tuyển 40+ ngành đào tạo năm 2026, đa dạng phương thức xét tuyển: Học bạ, Điểm thi TN THPT, Đánh giá năng lực, Xét tuyển CC ngoại ngữ...  Hiện tại nhà trường đang mở cổng ưu tiên đăng ký ghi danh sớm. Click vào link để đăng ký:</t>
-  </si>
-  <si>
     <t>1, Bạn đã chọn được ngành học chưa, mình đang quan tâm khối ngành nào để admin hỗ trợ chọn phương thức xét tuyển phù hợp nhất cho mình nhé!
 2. Nhà trường đang cấp học bổng khuyến học ưu tiên cho thí sinh đăng ký sớm. Bạn đã chọn được ngành học chưa, admin hỗ trợ mình đăng ký để ghi danh học bổng ưu tiên nhé!</t>
   </si>
   <si>
     <t>PTXT vào trường?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin chào ban, 
-ĐH Đông Á xét tuyển 40+ ngành đào tạo năm 2026, đa dạng phương thức xét tuyển: Học bạ, Điểm thi TN THPT, Đánh giá năng lực, Xét tuyển CC ngoại ngữ...  Chi tiết mời bạn tham khảo tại link sau, đội ngũ tư vấn viên sẽ hỗ trợ bạn liền nhé: </t>
   </si>
   <si>
     <t>https://donga.edu.vn/tuyensinh2026</t>
@@ -610,10 +595,6 @@
     <t>Khi nào trường bắt đầu nhận hồ sơ?</t>
   </si>
   <si>
-    <t>Admin chào bạn,
-Cảm ơn bạn đã liên hệ đến Đại học Đông Á. Cần hỗ trợ thông tin về Nhà trường, để lại câu hỏi để admin hỗ trợ bạn nhanh nhất nhé!</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <u/>
@@ -1969,12 +1950,30 @@
  • Tuy nhiên, Trường cam kết công khai toàn bộ mức học phí từ đầu khóa và không thay đổi trong suốt quá trình học, để sinh viên và phụ huynh yên tâm tài chính.
 </t>
   </si>
+  <si>
+    <t>Câu hỏi gợi mở</t>
+  </si>
+  <si>
+    <t>chào bạn,
+Cảm ơn bạn đã liên hệ đến Đại học Đông Á. Cần hỗ trợ thông tin về Nhà trường, để lại câu hỏi để admin hỗ trợ bạn nhanh nhất nhé!</t>
+  </si>
+  <si>
+    <t>chào ban, 
+ĐH Đông Á xét tuyển 40+ ngành đào tạo năm 2026, đa dạng phương thức xét tuyển: Học bạ, Điểm thi TN THPT, Đánh giá năng lực, Xét tuyển CC ngoại ngữ...  Hiện tại nhà trường đang mở cổng ưu tiên đăng ký ghi danh sớm. Click vào link để đăng ký:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chào ban, 
+ĐH Đông Á xét tuyển 40+ ngành đào tạo năm 2026, đa dạng phương thức xét tuyển: Học bạ, Điểm thi TN THPT, Đánh giá năng lực, Xét tuyển CC ngoại ngữ...  Chi tiết mời bạn tham khảo tại link sau, đội ngũ tư vấn viên sẽ hỗ trợ bạn liền nhé: </t>
+  </si>
+  <si>
+    <t>Đính kèm</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1985,10 +1984,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2128,7 +2123,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -2164,45 +2159,24 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2213,13 +2187,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2232,39 +2206,34 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2498,7 +2467,7 @@
     <col min="4" max="4" width="40.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
@@ -2506,333 +2475,349 @@
         <v>11</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>12</v>
+        <v>235</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>13</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="47.25" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>136</v>
+        <v>232</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
     </row>
-    <row r="3" spans="1:4" ht="63" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="78.75" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="157.5" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>19</v>
+        <v>233</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="267.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C6" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7" spans="1:4" ht="189" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="C7" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:4" ht="204.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="252" x14ac:dyDescent="0.2">
-      <c r="A6" s="27" t="s">
+      <c r="C8" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:4" ht="409.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C9" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" spans="1:4" ht="409.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C10" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:4" ht="330.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="D6" s="5"/>
-    </row>
-    <row r="7" spans="1:4" ht="173.25" x14ac:dyDescent="0.2">
-      <c r="A7" s="25"/>
-      <c r="B7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="6" t="s">
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:4" ht="346.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="D7" s="5"/>
-    </row>
-    <row r="8" spans="1:4" ht="189" x14ac:dyDescent="0.2">
-      <c r="A8" s="25"/>
-      <c r="B8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:4" ht="299.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:4" ht="409.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="25"/>
-      <c r="B9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="D9" s="5"/>
-    </row>
-    <row r="10" spans="1:4" ht="409.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="25"/>
-      <c r="B10" s="5" t="s">
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:4" ht="189" x14ac:dyDescent="0.2">
+      <c r="A14" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" spans="1:4" ht="330.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="25"/>
-      <c r="B11" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" spans="1:4" ht="330.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="25"/>
-      <c r="B12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13" spans="1:4" ht="283.5" x14ac:dyDescent="0.2">
-      <c r="A13" s="25"/>
-      <c r="B13" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="D13" s="5"/>
-    </row>
-    <row r="14" spans="1:4" ht="189" x14ac:dyDescent="0.2">
-      <c r="A14" s="26"/>
-      <c r="B14" s="5" t="s">
-        <v>34</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:4" ht="78.75" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="94.5" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="63" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="B16" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D16" s="4"/>
     </row>
     <row r="17" spans="1:4" ht="94.5" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C17" s="19"/>
       <c r="D17" s="19"/>
     </row>
     <row r="18" spans="1:4" ht="173.25" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C18" s="19"/>
       <c r="D18" s="19"/>
     </row>
     <row r="19" spans="1:4" ht="157.5" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C19" s="19"/>
       <c r="D19" s="19"/>
     </row>
     <row r="20" spans="1:4" ht="94.5" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C20" s="21"/>
       <c r="D20" s="21"/>
     </row>
     <row r="21" spans="1:4" ht="110.25" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C21" s="21"/>
       <c r="D21" s="21"/>
     </row>
     <row r="22" spans="1:4" ht="204.75" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C22" s="21"/>
       <c r="D22" s="21"/>
     </row>
     <row r="23" spans="1:4" ht="126" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C23" s="22"/>
       <c r="D23" s="22"/>
     </row>
     <row r="24" spans="1:4" ht="78.75" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C24" s="22"/>
       <c r="D24" s="5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="78.75" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
     </row>
     <row r="26" spans="1:4" ht="141.75" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C26" s="22"/>
       <c r="D26" s="22"/>
     </row>
     <row r="27" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C27" s="22"/>
       <c r="D27" s="22"/>
     </row>
     <row r="28" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C28" s="19"/>
       <c r="D28" s="19"/>
     </row>
     <row r="29" spans="1:4" ht="173.25" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D29" s="4"/>
     </row>
     <row r="30" spans="1:4" ht="47.25" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D30" s="4"/>
     </row>
     <row r="31" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="13" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D31" s="4"/>
     </row>
@@ -2848,74 +2833,74 @@
     </row>
     <row r="33" spans="1:4" ht="78.75" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
     </row>
     <row r="34" spans="1:4" ht="110.25" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D34" s="4"/>
     </row>
     <row r="35" spans="1:4" ht="94.5" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D35" s="4"/>
     </row>
     <row r="36" spans="1:4" ht="78.75" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D36" s="4"/>
     </row>
     <row r="37" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="141.75" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="63" x14ac:dyDescent="0.2">
@@ -2923,13 +2908,13 @@
         <v>3</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="110.25" x14ac:dyDescent="0.2">
@@ -2937,45 +2922,45 @@
         <v>4</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="63" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D41" s="4"/>
     </row>
     <row r="42" spans="1:4" ht="63" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D42" s="4"/>
     </row>
     <row r="43" spans="1:4" ht="47.25" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -2985,7 +2970,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -2995,7 +2980,7 @@
         <v>6</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
@@ -3005,27 +2990,27 @@
         <v>7</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
     </row>
     <row r="47" spans="1:4" ht="47.25" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
     </row>
     <row r="48" spans="1:4" ht="47.25" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
@@ -3035,251 +3020,251 @@
         <v>8</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D49" s="4"/>
     </row>
     <row r="50" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D50" s="4"/>
     </row>
     <row r="51" spans="1:4" ht="63" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
     </row>
     <row r="52" spans="1:4" ht="110.25" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D52" s="4"/>
     </row>
     <row r="53" spans="1:4" ht="110.25" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D53" s="4"/>
     </row>
     <row r="54" spans="1:4" ht="47.25" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D54" s="4"/>
     </row>
     <row r="55" spans="1:4" ht="78.75" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D55" s="4"/>
     </row>
     <row r="56" spans="1:4" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="4"/>
     </row>
     <row r="57" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D57" s="4"/>
     </row>
     <row r="58" spans="1:4" ht="63" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
     </row>
     <row r="59" spans="1:4" ht="63" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
     </row>
     <row r="60" spans="1:4" ht="63" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
     </row>
     <row r="61" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
     </row>
     <row r="62" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B62" s="20" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C62" s="19"/>
       <c r="D62" s="19"/>
     </row>
     <row r="63" spans="1:4" ht="63" x14ac:dyDescent="0.2">
       <c r="A63" s="9" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
     </row>
     <row r="64" spans="1:4" ht="126" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="5"/>
     </row>
     <row r="65" spans="1:4" ht="126" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
     </row>
     <row r="66" spans="1:4" ht="94.5" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C66" s="5"/>
       <c r="D66" s="5"/>
     </row>
     <row r="67" spans="1:4" ht="189" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
     </row>
     <row r="68" spans="1:4" ht="173.25" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
     </row>
     <row r="69" spans="1:4" ht="94.5" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
     </row>
     <row r="70" spans="1:4" ht="126" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
     </row>
     <row r="71" spans="1:4" ht="78.75" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
     </row>
     <row r="72" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C72" s="5"/>
       <c r="D72" s="5"/>
@@ -3289,402 +3274,446 @@
         <v>9</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
     </row>
     <row r="74" spans="1:4" ht="47.25" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
     </row>
     <row r="75" spans="1:4" ht="63" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D75" s="4"/>
     </row>
     <row r="76" spans="1:4" ht="94.5" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D76" s="4"/>
     </row>
     <row r="77" spans="1:4" ht="141.75" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C77" s="4"/>
       <c r="D77" s="24"/>
     </row>
     <row r="78" spans="1:4" ht="236.25" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C78" s="19"/>
       <c r="D78" s="19"/>
     </row>
     <row r="79" spans="1:4" ht="315" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C79" s="19"/>
       <c r="D79" s="19"/>
     </row>
     <row r="80" spans="1:4" ht="236.25" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C80" s="19"/>
       <c r="D80" s="19"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="B81" s="27" t="s">
-        <v>191</v>
+        <v>185</v>
+      </c>
+      <c r="B81" s="25" t="s">
+        <v>186</v>
       </c>
       <c r="C81" s="19"/>
       <c r="D81" s="19"/>
     </row>
-    <row r="82" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" ht="220.5" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="B82" s="25"/>
+        <v>187</v>
+      </c>
+      <c r="B82" s="25" t="s">
+        <v>186</v>
+      </c>
       <c r="C82" s="19"/>
       <c r="D82" s="19"/>
     </row>
     <row r="83" spans="1:4" ht="134.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="B83" s="26"/>
+        <v>188</v>
+      </c>
+      <c r="B83" s="25" t="s">
+        <v>186</v>
+      </c>
       <c r="C83" s="19"/>
       <c r="D83" s="19"/>
     </row>
     <row r="84" spans="1:4" ht="189" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C84" s="19"/>
       <c r="D84" s="19"/>
     </row>
     <row r="85" spans="1:4" ht="236.25" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C85" s="19"/>
       <c r="D85" s="19"/>
     </row>
     <row r="86" spans="1:4" ht="252" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C86" s="19"/>
       <c r="D86" s="19"/>
     </row>
     <row r="87" spans="1:4" ht="189" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C87" s="19"/>
       <c r="D87" s="19"/>
     </row>
     <row r="88" spans="1:4" ht="173.25" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C88" s="19"/>
       <c r="D88" s="19"/>
     </row>
     <row r="89" spans="1:4" ht="189" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C89" s="19"/>
       <c r="D89" s="19"/>
     </row>
-    <row r="90" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="B90" s="27" t="s">
-        <v>207</v>
+        <v>201</v>
+      </c>
+      <c r="B90" s="25" t="s">
+        <v>202</v>
       </c>
       <c r="C90" s="19"/>
       <c r="D90" s="19"/>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" ht="220.5" x14ac:dyDescent="0.2">
       <c r="A91" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="B91" s="25"/>
+        <v>203</v>
+      </c>
+      <c r="B91" s="25" t="s">
+        <v>202</v>
+      </c>
       <c r="C91" s="19"/>
       <c r="D91" s="19"/>
     </row>
-    <row r="92" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" ht="220.5" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="B92" s="25"/>
+        <v>204</v>
+      </c>
+      <c r="B92" s="25" t="s">
+        <v>202</v>
+      </c>
       <c r="C92" s="19"/>
       <c r="D92" s="19"/>
     </row>
-    <row r="93" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" ht="220.5" x14ac:dyDescent="0.2">
       <c r="A93" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="B93" s="25"/>
+        <v>205</v>
+      </c>
+      <c r="B93" s="25" t="s">
+        <v>202</v>
+      </c>
       <c r="C93" s="19"/>
       <c r="D93" s="19"/>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" ht="220.5" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="B94" s="25"/>
+        <v>206</v>
+      </c>
+      <c r="B94" s="25" t="s">
+        <v>202</v>
+      </c>
       <c r="C94" s="19"/>
       <c r="D94" s="19"/>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" ht="220.5" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="B95" s="25"/>
+        <v>207</v>
+      </c>
+      <c r="B95" s="25" t="s">
+        <v>202</v>
+      </c>
       <c r="C95" s="19"/>
       <c r="D95" s="19"/>
     </row>
-    <row r="96" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" ht="220.5" x14ac:dyDescent="0.2">
       <c r="A96" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="B96" s="25"/>
+        <v>208</v>
+      </c>
+      <c r="B96" s="25" t="s">
+        <v>202</v>
+      </c>
       <c r="C96" s="19"/>
       <c r="D96" s="19"/>
     </row>
-    <row r="97" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4" ht="220.5" x14ac:dyDescent="0.2">
       <c r="A97" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="B97" s="25"/>
+        <v>209</v>
+      </c>
+      <c r="B97" s="25" t="s">
+        <v>202</v>
+      </c>
       <c r="C97" s="19"/>
       <c r="D97" s="19"/>
     </row>
-    <row r="98" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4" ht="220.5" x14ac:dyDescent="0.2">
       <c r="A98" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="B98" s="25"/>
+        <v>210</v>
+      </c>
+      <c r="B98" s="25" t="s">
+        <v>202</v>
+      </c>
       <c r="C98" s="19"/>
       <c r="D98" s="19"/>
     </row>
-    <row r="99" spans="1:4" ht="47.25" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4" ht="220.5" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="B99" s="25"/>
+        <v>211</v>
+      </c>
+      <c r="B99" s="25" t="s">
+        <v>202</v>
+      </c>
       <c r="C99" s="19"/>
       <c r="D99" s="19"/>
     </row>
-    <row r="100" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4" ht="220.5" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B100" s="25"/>
+        <v>212</v>
+      </c>
+      <c r="B100" s="25" t="s">
+        <v>202</v>
+      </c>
       <c r="C100" s="19"/>
       <c r="D100" s="19"/>
     </row>
-    <row r="101" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4" ht="220.5" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="B101" s="25"/>
+        <v>213</v>
+      </c>
+      <c r="B101" s="25" t="s">
+        <v>202</v>
+      </c>
       <c r="C101" s="19"/>
       <c r="D101" s="19"/>
     </row>
-    <row r="102" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4" ht="220.5" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="B102" s="25"/>
+        <v>214</v>
+      </c>
+      <c r="B102" s="25" t="s">
+        <v>202</v>
+      </c>
       <c r="C102" s="19"/>
       <c r="D102" s="19"/>
     </row>
-    <row r="103" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4" ht="220.5" x14ac:dyDescent="0.2">
       <c r="A103" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="B103" s="25"/>
+        <v>215</v>
+      </c>
+      <c r="B103" s="25" t="s">
+        <v>202</v>
+      </c>
       <c r="C103" s="19"/>
       <c r="D103" s="19"/>
     </row>
-    <row r="104" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4" ht="220.5" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="B104" s="25"/>
+        <v>216</v>
+      </c>
+      <c r="B104" s="25" t="s">
+        <v>202</v>
+      </c>
       <c r="C104" s="19"/>
       <c r="D104" s="19"/>
     </row>
-    <row r="105" spans="1:4" ht="47.25" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4" ht="220.5" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="B105" s="25"/>
+        <v>217</v>
+      </c>
+      <c r="B105" s="25" t="s">
+        <v>202</v>
+      </c>
       <c r="C105" s="19"/>
       <c r="D105" s="19"/>
     </row>
-    <row r="106" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4" ht="220.5" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="B106" s="25"/>
+        <v>218</v>
+      </c>
+      <c r="B106" s="25" t="s">
+        <v>202</v>
+      </c>
       <c r="C106" s="19"/>
       <c r="D106" s="19"/>
     </row>
-    <row r="107" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4" ht="220.5" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="B107" s="25"/>
+        <v>219</v>
+      </c>
+      <c r="B107" s="25" t="s">
+        <v>202</v>
+      </c>
       <c r="C107" s="19"/>
       <c r="D107" s="19"/>
     </row>
-    <row r="108" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4" ht="220.5" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="B108" s="25"/>
+        <v>220</v>
+      </c>
+      <c r="B108" s="25" t="s">
+        <v>202</v>
+      </c>
       <c r="C108" s="19"/>
       <c r="D108" s="19"/>
     </row>
-    <row r="109" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4" ht="220.5" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B109" s="25"/>
+        <v>221</v>
+      </c>
+      <c r="B109" s="25" t="s">
+        <v>202</v>
+      </c>
       <c r="C109" s="19"/>
       <c r="D109" s="19"/>
     </row>
-    <row r="110" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4" ht="220.5" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="B110" s="25"/>
+        <v>222</v>
+      </c>
+      <c r="B110" s="25" t="s">
+        <v>202</v>
+      </c>
       <c r="C110" s="19"/>
       <c r="D110" s="19"/>
     </row>
-    <row r="111" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4" ht="220.5" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="B111" s="25"/>
+        <v>223</v>
+      </c>
+      <c r="B111" s="25" t="s">
+        <v>202</v>
+      </c>
       <c r="C111" s="19"/>
       <c r="D111" s="19"/>
     </row>
-    <row r="112" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4" ht="220.5" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="B112" s="26"/>
+        <v>224</v>
+      </c>
+      <c r="B112" s="25" t="s">
+        <v>202</v>
+      </c>
       <c r="C112" s="19"/>
       <c r="D112" s="19"/>
     </row>
     <row r="113" spans="1:4" ht="189" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C113" s="19"/>
       <c r="D113" s="19"/>
     </row>
-    <row r="114" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="B114" s="27" t="s">
-        <v>233</v>
+        <v>227</v>
+      </c>
+      <c r="B114" s="25" t="s">
+        <v>228</v>
       </c>
       <c r="C114" s="19"/>
       <c r="D114" s="19"/>
     </row>
     <row r="115" spans="1:4" ht="121.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="B115" s="26"/>
+        <v>229</v>
+      </c>
+      <c r="B115" s="25" t="s">
+        <v>228</v>
+      </c>
       <c r="C115" s="19"/>
       <c r="D115" s="19"/>
     </row>
     <row r="116" spans="1:4" ht="236.25" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C116" s="19"/>
       <c r="D116" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A6:A14"/>
-    <mergeCell ref="B90:B112"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="B81:B83"/>
-  </mergeCells>
   <hyperlinks>
     <hyperlink ref="C3" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
     <hyperlink ref="C4" r:id="rId2" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
@@ -3721,5 +3750,6 @@
     <hyperlink ref="B73" r:id="rId33" xr:uid="{00000000-0004-0000-0500-000020000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId34"/>
 </worksheet>
 </file>